--- a/Configs/GameConfig/Datas/event.xlsx
+++ b/Configs/GameConfig/Datas/event.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R812d7af4b35a41d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd3eccc6bcbd497e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,12 +334,8 @@
       <x:c r="B1" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="C1" t="str">
-        <x:v>eventName</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>code</x:v>
-      </x:c>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -348,12 +344,8 @@
       <x:c r="B2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C2" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>string</x:v>
-      </x:c>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -368,266 +360,178 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C4" t="str">
-        <x:v>事件名(主键)</x:v>
-      </x:c>
-      <x:c r="D4" t="str">
-        <x:v>事件码</x:v>
-      </x:c>
+        <x:v>主键</x:v>
+      </x:c>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
       <x:c r="B5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>BATTLE_FINISHED</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>l</x:v>
-      </x:c>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
       <x:c r="B6" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C6" t="str">
-        <x:v>ROUND_STARTED</x:v>
-      </x:c>
-      <x:c r="D6" t="str">
-        <x:v>Ft</x:v>
-      </x:c>
+      <x:c r="C6"/>
+      <x:c r="D6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
       <x:c r="B7" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" t="str">
-        <x:v>ROUND_SPAWN_PREPARED</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>Jt</x:v>
-      </x:c>
+      <x:c r="C7"/>
+      <x:c r="D7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
       <x:c r="B8" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C8" t="str">
-        <x:v>BATTLE_SCENE_GAME_OVER</x:v>
-      </x:c>
-      <x:c r="D8" t="str">
-        <x:v>It</x:v>
-      </x:c>
+      <x:c r="C8"/>
+      <x:c r="D8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
       <x:c r="B9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C9" t="str">
-        <x:v>BATTLE_RESULT_READY</x:v>
-      </x:c>
-      <x:c r="D9" t="str">
-        <x:v>o</x:v>
-      </x:c>
+      <x:c r="C9"/>
+      <x:c r="D9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
       <x:c r="B10" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" t="str">
-        <x:v>HEALTH_CHANGED</x:v>
-      </x:c>
-      <x:c r="D10" t="str">
-        <x:v>Ct</x:v>
-      </x:c>
+      <x:c r="C10"/>
+      <x:c r="D10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
       <x:c r="B11" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C11" t="str">
-        <x:v>GOLD_CHANGED</x:v>
-      </x:c>
-      <x:c r="D11" t="str">
-        <x:v>Dt</x:v>
-      </x:c>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
       <x:c r="B12" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C12" t="str">
-        <x:v>ENEMY_CREATED</x:v>
-      </x:c>
-      <x:c r="D12" t="str">
-        <x:v>Ht</x:v>
-      </x:c>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
       <x:c r="B13" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C13" t="str">
-        <x:v>ENEMY_REGISTERED</x:v>
-      </x:c>
-      <x:c r="D13" t="str">
-        <x:v>nt</x:v>
-      </x:c>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C14" t="str">
-        <x:v>ENEMY_REMOVED</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>ot</x:v>
-      </x:c>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C15" t="str">
-        <x:v>ENEMY_GRID_LEFT</x:v>
-      </x:c>
-      <x:c r="D15" t="str">
-        <x:v>ft</x:v>
-      </x:c>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
       <x:c r="B16" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C16" t="str">
-        <x:v>ENEMY_VISUAL_ADDED</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>bt</x:v>
-      </x:c>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17"/>
       <x:c r="B17" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C17" t="str">
-        <x:v>ENEMY_GRID_ENTERED</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>vt</x:v>
-      </x:c>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C18" t="str">
-        <x:v>ENEMY_GRID_ENTITY_ENTERED</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>_t</x:v>
-      </x:c>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C19" t="str">
-        <x:v>ENEMY_KILLED_BY</x:v>
-      </x:c>
-      <x:c r="D19" t="str">
-        <x:v>ht</x:v>
-      </x:c>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C20" t="str">
-        <x:v>ENEMY_APPROACH_WARNING</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>kt</x:v>
-      </x:c>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C21" t="str">
-        <x:v>ENEMY_FINAL_WARNING</x:v>
-      </x:c>
-      <x:c r="D21" t="str">
-        <x:v>wt</x:v>
-      </x:c>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C22" t="str">
-        <x:v>SKILL_EFFECT_REQUESTED</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>skill:effect:requested</x:v>
-      </x:c>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C23" t="str">
-        <x:v>BOSS_SPAWNED</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>boss:spawned</x:v>
-      </x:c>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C24" t="str">
-        <x:v>BOSS_REMOVED</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>boss:removed</x:v>
-      </x:c>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C25" t="str">
-        <x:v>WAVE_PLANNED</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>wave:planned</x:v>
-      </x:c>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
